--- a/research/traditional_assets/database/data/philippines/philippines_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_investments_asset_management.xlsx
@@ -587,8 +587,11 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="E2">
+        <v>0.009220000000000001</v>
+      </c>
       <c r="K2">
-        <v>3.246</v>
+        <v>1.242</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,70 +615,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.994</v>
+        <v>5.382000000000001</v>
       </c>
       <c r="V2">
-        <v>0.04676029962546816</v>
+        <v>0.06571428571428571</v>
       </c>
       <c r="W2">
-        <v>-0.007272727272727272</v>
+        <v>-0.0002145922746781116</v>
       </c>
       <c r="X2">
-        <v>0.05741399390453115</v>
+        <v>0.09115449731022837</v>
       </c>
       <c r="Y2">
-        <v>-0.06468672117725842</v>
+        <v>-0.09136908958490648</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.09485094850948511</v>
+        <v>-0.7249999999999833</v>
       </c>
       <c r="AB2">
-        <v>0.05741399390453115</v>
+        <v>0.09115449731022837</v>
       </c>
       <c r="AC2">
-        <v>-0.1522649424140163</v>
+        <v>-0.8161544973102117</v>
       </c>
       <c r="AD2">
-        <v>32.7</v>
+        <v>28.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>32.7</v>
+        <v>28.7</v>
       </c>
       <c r="AG2">
-        <v>27.706</v>
+        <v>23.318</v>
       </c>
       <c r="AH2">
-        <v>0.2344086021505377</v>
+        <v>0.2594936708860759</v>
       </c>
       <c r="AI2">
-        <v>0.5423065441639856</v>
+        <v>0.5170239596469105</v>
       </c>
       <c r="AJ2">
-        <v>0.2059833762062659</v>
+        <v>0.2216160732954437</v>
       </c>
       <c r="AK2">
-        <v>0.5009764212353537</v>
+        <v>0.4651691669326524</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.035</v>
+        <v>-0.049</v>
       </c>
       <c r="AN2">
-        <v>-165.9898477157361</v>
+        <v>-318.8888888888889</v>
       </c>
       <c r="AP2">
-        <v>-140.6395939086295</v>
+        <v>-259.0888888888889</v>
       </c>
       <c r="AQ2">
-        <v>11.05714285714286</v>
+        <v>3.816326530612245</v>
       </c>
     </row>
     <row r="3">
@@ -694,8 +697,11 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="E3">
+        <v>0.009220000000000001</v>
+      </c>
       <c r="K3">
-        <v>3.32</v>
+        <v>1.28</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -719,67 +725,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.004</v>
+        <v>1.1</v>
       </c>
       <c r="V3">
-        <v>8.016032064128257e-05</v>
+        <v>0.02669902912621359</v>
       </c>
       <c r="W3">
-        <v>0.1627450980392157</v>
+        <v>0.05663716814159292</v>
       </c>
       <c r="X3">
-        <v>0.07682416064751148</v>
+        <v>0.1185071806743708</v>
       </c>
       <c r="Y3">
-        <v>0.08592093739170421</v>
+        <v>-0.06187001253277784</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.00428183590547164</v>
+        <v>-0.002152054398148148</v>
       </c>
       <c r="AB3">
-        <v>0.05949274604706782</v>
+        <v>0.09513060410317022</v>
       </c>
       <c r="AC3">
-        <v>-0.06377458195253946</v>
+        <v>-0.09728265850131837</v>
       </c>
       <c r="AD3">
-        <v>32.7</v>
+        <v>28.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>32.7</v>
+        <v>28.7</v>
       </c>
       <c r="AG3">
-        <v>32.69600000000001</v>
+        <v>27.6</v>
       </c>
       <c r="AH3">
-        <v>0.3958837772397095</v>
+        <v>0.4105865522174534</v>
       </c>
       <c r="AI3">
-        <v>0.5913200723327305</v>
+        <v>0.5786290322580646</v>
       </c>
       <c r="AJ3">
-        <v>0.3958545208000388</v>
+        <v>0.4011627906976744</v>
       </c>
       <c r="AK3">
-        <v>0.5912905092592593</v>
+        <v>0.5690721649484536</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="AN3">
-        <v>-165.9898477157361</v>
+        <v>-318.8888888888889</v>
       </c>
       <c r="AP3">
-        <v>-165.9695431472081</v>
+        <v>-306.6666666666666</v>
+      </c>
+      <c r="AQ3">
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -790,7 +799,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pacifica Holdings, Inc. (PSE:PA)</t>
+          <t>Lodestar Investment Holdings Corporation (PSE:LODE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -799,7 +808,7 @@
         </is>
       </c>
       <c r="K4">
-        <v>-0.038</v>
+        <v>-0.001</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -823,31 +832,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.35</v>
+        <v>4.03</v>
       </c>
       <c r="V4">
-        <v>0.01732673267326732</v>
+        <v>0.1361486486486486</v>
       </c>
       <c r="W4">
-        <v>-0.09595959595959595</v>
+        <v>-0.0002145922746781116</v>
       </c>
       <c r="X4">
-        <v>0.05741399390453115</v>
+        <v>0.09115449731022837</v>
       </c>
       <c r="Y4">
-        <v>-0.1533735898641271</v>
+        <v>-0.09136908958490648</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>-0.09485094850948511</v>
+        <v>-0.7249999999999833</v>
       </c>
       <c r="AB4">
-        <v>0.05741399390453115</v>
+        <v>0.09115449731022837</v>
       </c>
       <c r="AC4">
-        <v>-0.1522649424140163</v>
+        <v>-0.8161544973102117</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -859,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-0.35</v>
+        <v>-4.03</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -868,16 +877,19 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.01763224181360202</v>
+        <v>-0.1576065701994525</v>
       </c>
       <c r="AK4">
-        <v>29.16666666666677</v>
+        <v>-134.3333333333362</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-0.037</v>
+      </c>
+      <c r="AQ4">
+        <v>0.7837837837837839</v>
       </c>
     </row>
     <row r="5">
@@ -888,7 +900,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lodestar Investment Holdings Corporation (PSE:LODE)</t>
+          <t>Pacifica Holdings, Inc. (PSE:PA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -897,7 +909,7 @@
         </is>
       </c>
       <c r="K5">
-        <v>-0.036</v>
+        <v>-0.037</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -921,31 +933,22 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>4.64</v>
+        <v>0.252</v>
       </c>
       <c r="V5">
-        <v>0.1264305177111716</v>
+        <v>0.0227027027027027</v>
       </c>
       <c r="W5">
-        <v>-0.007272727272727272</v>
+        <v>-0.1094674556213018</v>
       </c>
       <c r="X5">
-        <v>0.05741399390453115</v>
+        <v>0.09115449731022837</v>
       </c>
       <c r="Y5">
-        <v>-0.06468672117725842</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>-1.462499999999999</v>
+        <v>-0.2006219529315301</v>
       </c>
       <c r="AB5">
-        <v>0.05741399390453115</v>
-      </c>
-      <c r="AC5">
-        <v>-1.51991399390453</v>
+        <v>0.09115449731022837</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -957,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-4.64</v>
+        <v>-0.252</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -966,19 +969,19 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.1447286338116032</v>
+        <v>-0.02323008849557522</v>
       </c>
       <c r="AK5">
-        <v>-231.9999999999946</v>
+        <v>-0.1576971214017522</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.035</v>
+        <v>-0.005</v>
       </c>
       <c r="AQ5">
-        <v>3.342857142857143</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/philippines/philippines_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,11 +587,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="E2">
-        <v>0.009220000000000001</v>
+      <c r="D2">
+        <v>-5e-05</v>
+      </c>
+      <c r="G2">
+        <v>-1.867924528301887</v>
+      </c>
+      <c r="H2">
+        <v>-1.867924528301887</v>
+      </c>
+      <c r="I2">
+        <v>-5.566037735849056</v>
+      </c>
+      <c r="J2">
+        <v>-5.566037735849056</v>
       </c>
       <c r="K2">
-        <v>1.242</v>
+        <v>-0.08</v>
+      </c>
+      <c r="L2">
+        <v>-1.509433962264151</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -600,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -609,76 +624,76 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.382000000000001</v>
+        <v>5.021999999999999</v>
       </c>
       <c r="V2">
-        <v>0.06571428571428571</v>
+        <v>0.06437636200487115</v>
       </c>
       <c r="W2">
-        <v>-0.0002145922746781116</v>
+        <v>-0.00500766021637165</v>
       </c>
       <c r="X2">
-        <v>0.09115449731022837</v>
+        <v>0.0765394177116222</v>
       </c>
       <c r="Y2">
-        <v>-0.09136908958490648</v>
+        <v>-0.08154707792799386</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>0.00102306727149889</v>
       </c>
       <c r="AA2">
-        <v>-0.7249999999999833</v>
+        <v>-0.02077346683354193</v>
       </c>
       <c r="AB2">
-        <v>0.09115449731022837</v>
+        <v>0.0765394177116222</v>
       </c>
       <c r="AC2">
-        <v>-0.8161544973102117</v>
+        <v>-0.09849631177705678</v>
       </c>
       <c r="AD2">
-        <v>28.7</v>
+        <v>29.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>28.7</v>
+        <v>29.5</v>
       </c>
       <c r="AG2">
-        <v>23.318</v>
+        <v>24.478</v>
       </c>
       <c r="AH2">
-        <v>0.2594936708860759</v>
+        <v>0.274393079713515</v>
       </c>
       <c r="AI2">
-        <v>0.5170239596469105</v>
+        <v>0.4998305659098611</v>
       </c>
       <c r="AJ2">
-        <v>0.2216160732954437</v>
+        <v>0.2388377175864492</v>
       </c>
       <c r="AK2">
-        <v>0.4651691669326524</v>
+        <v>0.4533130856698396</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.049</v>
+        <v>-0.057</v>
       </c>
       <c r="AN2">
-        <v>-318.8888888888889</v>
+        <v>-179.8780487804878</v>
       </c>
       <c r="AP2">
-        <v>-259.0888888888889</v>
+        <v>-149.2560975609756</v>
       </c>
       <c r="AQ2">
-        <v>3.816326530612245</v>
+        <v>5.175438596491228</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bright Kindle Resources &amp; Investments, Inc. (PSE:BKR)</t>
+          <t>BHI Holdings, Inc. (PSE:BH)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -697,11 +712,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="E3">
-        <v>0.009220000000000001</v>
+      <c r="D3">
+        <v>-5e-05</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0.1320754716981132</v>
+      </c>
+      <c r="J3">
+        <v>0.1320754716981132</v>
       </c>
       <c r="K3">
-        <v>1.28</v>
+        <v>0.007</v>
+      </c>
+      <c r="L3">
+        <v>0.1320754716981132</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -725,70 +755,61 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.1</v>
+        <v>0.003</v>
       </c>
       <c r="V3">
-        <v>0.02669902912621359</v>
+        <v>0.0004909983633387888</v>
       </c>
       <c r="W3">
-        <v>0.05663716814159292</v>
+        <v>0.004166666666666667</v>
       </c>
       <c r="X3">
-        <v>0.1185071806743708</v>
+        <v>0.0765394177116222</v>
       </c>
       <c r="Y3">
-        <v>-0.06187001253277784</v>
+        <v>-0.07237275104495554</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>0.03160405485986881</v>
       </c>
       <c r="AA3">
-        <v>-0.002152054398148148</v>
+        <v>0.004174120453190221</v>
       </c>
       <c r="AB3">
-        <v>0.09513060410317022</v>
+        <v>0.0765394177116222</v>
       </c>
       <c r="AC3">
-        <v>-0.09728265850131837</v>
+        <v>-0.07236529725843198</v>
       </c>
       <c r="AD3">
-        <v>28.7</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>28.7</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>27.6</v>
+        <v>-0.003</v>
       </c>
       <c r="AH3">
-        <v>0.4105865522174534</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.5786290322580646</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.4011627906976744</v>
+        <v>-0.0004912395611593254</v>
       </c>
       <c r="AK3">
-        <v>0.5690721649484536</v>
+        <v>-0.001717229536348025</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.007</v>
-      </c>
-      <c r="AN3">
-        <v>-318.8888888888889</v>
-      </c>
-      <c r="AP3">
-        <v>-306.6666666666666</v>
-      </c>
-      <c r="AQ3">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -799,7 +820,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lodestar Investment Holdings Corporation (PSE:LODE)</t>
+          <t>Bright Kindle Resources &amp; Investments, Inc. (PSE:BKR)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -808,88 +829,94 @@
         </is>
       </c>
       <c r="K4">
+        <v>-0.024</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.663</v>
+      </c>
+      <c r="V4">
+        <v>0.01717616580310881</v>
+      </c>
+      <c r="W4">
+        <v>-0.001148325358851675</v>
+      </c>
+      <c r="X4">
+        <v>0.09817114353726057</v>
+      </c>
+      <c r="Y4">
+        <v>-0.09931946889611225</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>-0.004000000000000001</v>
+      </c>
+      <c r="AB4">
+        <v>0.07890627217540749</v>
+      </c>
+      <c r="AC4">
+        <v>-0.0829062721754075</v>
+      </c>
+      <c r="AD4">
+        <v>29.5</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>29.5</v>
+      </c>
+      <c r="AG4">
+        <v>28.837</v>
+      </c>
+      <c r="AH4">
+        <v>0.433186490455213</v>
+      </c>
+      <c r="AI4">
+        <v>0.576171875</v>
+      </c>
+      <c r="AJ4">
+        <v>0.4276139211412133</v>
+      </c>
+      <c r="AK4">
+        <v>0.5706116310821774</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
         <v>-0.001</v>
       </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>4.03</v>
-      </c>
-      <c r="V4">
-        <v>0.1361486486486486</v>
-      </c>
-      <c r="W4">
-        <v>-0.0002145922746781116</v>
-      </c>
-      <c r="X4">
-        <v>0.09115449731022837</v>
-      </c>
-      <c r="Y4">
-        <v>-0.09136908958490648</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>-0.7249999999999833</v>
-      </c>
-      <c r="AB4">
-        <v>0.09115449731022837</v>
-      </c>
-      <c r="AC4">
-        <v>-0.8161544973102117</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>-4.03</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.1576065701994525</v>
-      </c>
-      <c r="AK4">
-        <v>-134.3333333333362</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>-0.037</v>
+      <c r="AN4">
+        <v>-179.8780487804878</v>
+      </c>
+      <c r="AP4">
+        <v>-175.8353658536585</v>
       </c>
       <c r="AQ4">
-        <v>0.7837837837837839</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5">
@@ -909,7 +936,7 @@
         </is>
       </c>
       <c r="K5">
-        <v>-0.037</v>
+        <v>-0.027</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -933,22 +960,31 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.252</v>
+        <v>0.216</v>
       </c>
       <c r="V5">
-        <v>0.0227027027027027</v>
+        <v>0.02666666666666667</v>
       </c>
       <c r="W5">
-        <v>-0.1094674556213018</v>
+        <v>-0.01459459459459459</v>
       </c>
       <c r="X5">
-        <v>0.09115449731022837</v>
+        <v>0.0765394177116222</v>
       </c>
       <c r="Y5">
-        <v>-0.2006219529315301</v>
+        <v>-0.0911340123062168</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>-0.03754693366708385</v>
       </c>
       <c r="AB5">
-        <v>0.09115449731022837</v>
+        <v>0.0765394177116222</v>
+      </c>
+      <c r="AC5">
+        <v>-0.1140863513787061</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -960,7 +996,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-0.252</v>
+        <v>-0.216</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -969,19 +1005,120 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.02323008849557522</v>
+        <v>-0.0273972602739726</v>
       </c>
       <c r="AK5">
-        <v>-0.1576971214017522</v>
+        <v>-0.1282660332541568</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.005</v>
+        <v>-0.033</v>
       </c>
       <c r="AQ5">
-        <v>7.8</v>
+        <v>1.818181818181818</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Lodestar Investment Holdings Corporation (PSE:LODE)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K6">
+        <v>-0.036</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>4.14</v>
+      </c>
+      <c r="V6">
+        <v>0.1642857142857143</v>
+      </c>
+      <c r="W6">
+        <v>-0.008866995073891626</v>
+      </c>
+      <c r="X6">
+        <v>0.0765394177116222</v>
+      </c>
+      <c r="Y6">
+        <v>-0.08540641278551384</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>-1.600000000000034</v>
+      </c>
+      <c r="AB6">
+        <v>0.0765394177116222</v>
+      </c>
+      <c r="AC6">
+        <v>-1.676539417711656</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>-4.14</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.1965811965811966</v>
+      </c>
+      <c r="AK6">
+        <v>-137.9999999999988</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>-0.023</v>
+      </c>
+      <c r="AQ6">
+        <v>2.08695652173913</v>
       </c>
     </row>
   </sheetData>
